--- a/WorkBot/refactor/data/orders/Equal Exchange/Equal Exchange_Easthill_2025-10-10.xlsx
+++ b/WorkBot/refactor/data/orders/Equal Exchange/Equal Exchange_Easthill_2025-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,33 +521,6 @@
       <c r="E4" t="inlineStr">
         <is>
           <t>77.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>10400</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Equal Exchange - One World</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>77.50</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>232.50</t>
         </is>
       </c>
     </row>
